--- a/output/pdf_financials_xlsx/AURA.xlsx
+++ b/output/pdf_financials_xlsx/AURA.xlsx
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.568547</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.154911</v>
       </c>
     </row>
     <row r="93">
@@ -2528,7 +2528,11 @@
           <t>Reserves (notes 10 and 11)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>1.568547</v>
       </c>

--- a/output/pdf_financials_xlsx/AURA.xlsx
+++ b/output/pdf_financials_xlsx/AURA.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.07657600000000001</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
         <v>-1.282317</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.38597</v>
+        <v>-12.462546</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         <v>-1.282317</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.38597</v>
+        <v>-12.462546</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.781014</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.389284</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.781014</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.389284</v>
       </c>
     </row>
     <row r="37">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
